--- a/notebooks/tables/means.xlsx
+++ b/notebooks/tables/means.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,28 +482,84 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>TransformerTimestamps</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTime2Vec</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>TransformerPE</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>0.89</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>0.87</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>0.84</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
         <v>0.79</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>0.74</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G5" t="n">
         <v>0.68</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H5" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>

--- a/notebooks/tables/means.xlsx
+++ b/notebooks/tables/means.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,112 +454,616 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>RNN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="C2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.82</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.76</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="G2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>TransformerTimestamps</t>
+          <t>RNNTimestamps</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
         <v>0.74</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TransformerTime2Vec</t>
+          <t>RNNTimestampsRel</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="C4" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="D4" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="F4" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="G4" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>RNNTime2Vec</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>RNNPE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>RNNTPE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>RNNLinear</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>RNNTime2VecRel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>RNNPERel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>RNNTPERel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>RNNLinearRel</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTimestamps</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTimestampsRel</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTime2Vec</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>TransformerPE</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C17" t="n">
         <v>0.89</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="D17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTPE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.84</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>TransformerLinear</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTime2VecRel</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.79</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>TransformerPERel</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>TransformerTPERel</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>TransformerLinearRel</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.68</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H23" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
